--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -335,7 +335,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7315200" cy="4114800"/>
+    <ext cx="8229600" cy="4572000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -357,6 +357,36 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10058400" cy="5029200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -386,7 +416,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -395,7 +425,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9144000" cy="4114800"/>
+    <ext cx="8229600" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -416,7 +446,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -425,7 +455,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10058400" cy="4114800"/>
+    <ext cx="10058400" cy="4572000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -446,36 +476,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9144000" cy="4114800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -485,7 +485,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11887200" cy="8229600"/>
+    <ext cx="11887200" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>折れ線 + 面</t>
+          <t>折れ線 + 面（3系列）</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>縦棒グラフ</t>
+          <t>積み上げ棒グラフ</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>円グラフ + 横棒</t>
+          <t>円グラフ</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>グループ棒グラフ</t>
+          <t>二重軸グラフ</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>箱ひげ図 + 棒グラフ</t>
+          <t>箱ひげ図（昼・夜）</t>
         </is>
       </c>
     </row>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -365,7 +365,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10058400" cy="5029200"/>
+    <ext cx="9144000" cy="5943600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -395,7 +395,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7315200" cy="5029200"/>
+    <ext cx="7315200" cy="5486400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -425,7 +425,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8229600" cy="5029200"/>
+    <ext cx="5486400" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -40,32 +40,32 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000b4ff"/>
+      <color rgb="0000c8ff"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000b4ff"/>
+      <color rgb="0000c8ff"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ff9f1c"/>
+      <color rgb="00ffb020"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ff9f1c"/>
+      <color rgb="00ffb020"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009b5de5"/>
+      <color rgb="00a855f7"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009b5de5"/>
+      <color rgb="00a855f7"/>
       <sz val="14"/>
     </font>
     <font>
@@ -305,7 +305,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10058400" cy="4114800"/>
+    <ext cx="10972800" cy="4572000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -335,7 +335,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8229600" cy="4572000"/>
+    <ext cx="8229600" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -455,7 +455,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10058400" cy="4572000"/>
+    <ext cx="10058400" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -485,7 +485,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="11887200" cy="5029200"/>
+    <ext cx="12801600" cy="5486400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -515,7 +515,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10058400" cy="4114800"/>
+    <ext cx="10972800" cy="4572000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -831,7 +831,7 @@
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -947,7 +947,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>折れ線 + 面（3系列）</t>
+          <t>折れ線 + 面（グロウ）</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>箱ひげ図（昼・夜）</t>
+          <t>箱ひげ図 + 散布点</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>折れ線グラフ</t>
+          <t>折れ線グラフ（グロウ）</t>
         </is>
       </c>
     </row>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -485,7 +485,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="12801600" cy="5486400"/>
+    <ext cx="11887200" cy="5029200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -365,7 +365,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9144000" cy="5943600"/>
+    <ext cx="10058400" cy="6400800"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 天気別 売上分布" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑦ FOOD・DRINK ランキング" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑨ 客単価 日次推移" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑩ 相関行列ヒートマップ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑪ 散布図＋回帰直線" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -326,6 +328,36 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10058400" cy="7315200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -516,6 +548,36 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="10972800" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8229600" cy="6858000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -825,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L15"/>
+  <dimension ref="B1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1118,36 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>⑩ 相関行列ヒートマップ</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>ヒートマップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>⑪ 散布図＋回帰直線</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>散布図</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="F3:G3"/>
@@ -1075,6 +1167,56 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>⑩ 相関行列ヒートマップ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>⑪ 散布図＋回帰直線</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -15,9 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 昼食 vs 夕食" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 天気別 売上分布" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑦ FOOD・DRINK ランキング" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑨ 客単価 日次推移" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑩ 相関行列ヒートマップ" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑪ 散布図＋回帰直線" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑧ 客単価 日次推移" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -328,36 +326,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10058400" cy="7315200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -548,36 +516,6 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="10972800" cy="4572000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8229600" cy="6858000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -887,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L17"/>
+  <dimension ref="B1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1109,42 +1047,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>⑨ 客単価 日次推移</t>
+          <t>⑧ 客単価 日次推移</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
           <t>折れ線グラフ（グロウ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="B16" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>⑩ 相関行列ヒートマップ</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>ヒートマップ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>⑪ 散布図＋回帰直線</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>散布図</t>
         </is>
       </c>
     </row>
@@ -1167,56 +1075,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>⑩ 相関行列ヒートマップ</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>⑪ 散布図＋回帰直線</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1404,7 +1262,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>⑨ 客単価 日次推移</t>
+          <t>⑧ 客単価 日次推移</t>
         </is>
       </c>
     </row>

--- a/frontend/public/data/report_2026_5.xlsx
+++ b/frontend/public/data/report_2026_5.xlsx
@@ -9,13 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="① 日次売上トレンド" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② 曜日別 平均売上" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 支払方法別 構成" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④ カテゴリ別 構成" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤ 昼食 vs 夕食" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 天気別 売上分布" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑦ FOOD・DRINK ランキング" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑧ 客単価 日次推移" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="② カテゴリ別 構成" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="③ 曜日別 平均売上" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="④⑤ FOOD・DRINK ランキング" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥ 客単価 日次推移" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑦ 支払方法別 構成" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,70 +33,80 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B4FF"/>
+      <color rgb="000284C7"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000c8ff"/>
+      <color rgb="000284c7"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000c8ff"/>
+      <color rgb="000284c7"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ffb020"/>
+      <color rgb="00059669"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ffb020"/>
+      <color rgb="00059669"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00a855f7"/>
+      <color rgb="00d97706"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00a855f7"/>
+      <color rgb="00d97706"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000ecec"/>
+      <color rgb="007c3aed"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000ecec"/>
+      <color rgb="007c3aed"/>
       <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000F5A0"/>
+      <color rgb="000891b2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000891b2"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000284C7"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B4FF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D0E8FF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="004A6A8A"/>
+      <color rgb="000F172A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00475569"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -107,16 +115,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0008123A"/>
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00030718"/>
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000284C7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -125,99 +143,175 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right style="medium">
+        <color rgb="000284C7"/>
+      </right>
+      <top style="medium">
+        <color rgb="000284C7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000284C7"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="000284c7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000284c7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00059669"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00059669"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00d97706"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00d97706"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="007c3aed"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="007c3aed"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="000891b2"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000891b2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="000F2D4A"/>
+        <color rgb="00CBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="000F2D4A"/>
+        <color rgb="00CBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="000F2D4A"/>
+        <color rgb="00CBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="000F2D4A"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="000F2D4A"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000F2D4A"/>
-      </right>
-      <top style="thin">
-        <color rgb="000F2D4A"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="000F2D4A"/>
-      </right>
-      <top style="thin">
-        <color rgb="000F2D4A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="000F2D4A"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="00CBD5E1"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -302,7 +396,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10972800" cy="4572000"/>
@@ -332,7 +426,37 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7315200" cy="5486400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8229600" cy="5029200"/>
@@ -356,133 +480,13 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10058400" cy="6400800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7315200" cy="5486400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5486400" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10058400" cy="5029200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="11887200" cy="5029200"/>
@@ -506,16 +510,46 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>0</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="10972800" cy="4572000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9144000" cy="3200400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -822,10 +856,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L15"/>
+  <dimension ref="B1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -857,202 +892,172 @@
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>総来客数</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>平均客単価</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
           <t>FOOD売上</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>DRINK売上</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>総来客数</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>稼働日数</t>
         </is>
       </c>
-      <c r="K3" s="3" t="n"/>
+      <c r="K3" s="11" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>¥2099万円</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>¥1498万円</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>¥300万円</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="9" t="inlineStr">
+    <row r="4" ht="32" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2099万円</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>4,054名</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>5,178円</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n"/>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>1498万円</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="n"/>
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>27日</t>
         </is>
       </c>
-      <c r="K4" s="3" t="n"/>
+      <c r="K4" s="13" t="n"/>
     </row>
-    <row r="6">
-      <c r="B6" s="11" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>■ 分析チャート一覧</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>チャート名</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>グラフ種類</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>① 日次売上トレンド</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>折れ線 + 面（グロウ）</t>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>折れ線 + 面</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>② 曜日別 平均売上</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>積み上げ棒グラフ</t>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>② カテゴリ別 構成</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>円グラフ</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>③ 支払方法別 構成</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>ドーナツグラフ</t>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>③ 曜日別 平均売上</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>積み上げ棒グラフ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>④ カテゴリ別 構成</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>円グラフ</t>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>④⑤ FOOD・DRINK ランキング</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>横棒グラフ</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>⑤ 昼食 vs 夕食</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>二重軸グラフ</t>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>⑥ 客単価 日次推移</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>折れ線グラフ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>⑥ 天気別 売上分布</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>箱ひげ図 + 散布点</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>⑦ FOOD・DRINK ランキング</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>横棒グラフ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>⑧ 客単価 日次推移</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>折れ線グラフ（グロウ）</t>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>⑦ 支払方法別 構成</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>100%積み上げ横棒</t>
         </is>
       </c>
     </row>
@@ -1078,23 +1083,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>① 日次売上トレンド</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1103,23 +1098,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>② 曜日別 平均売上</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1128,23 +1113,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>③ 支払方法別 構成</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1153,23 +1128,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>④ カテゴリ別 構成</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1178,23 +1143,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>⑤ 昼食 vs 夕食</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1203,73 +1158,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>⑥ 天気別 売上分布</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>⑦ FOOD・DRINK ランキング</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>⑧ 客単価 日次推移</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
